--- a/docs/[产线控制软件V0]数据模型.xlsx
+++ b/docs/[产线控制软件V0]数据模型.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t/>
   </si>
@@ -894,6 +894,24 @@
   </si>
   <si>
     <t>下单日期，类型：int</t>
+  </si>
+  <si>
+    <t>8Pro-01，格式：PP-{SKU}-{PATTERN_KEY}-{SIZE_KEY}-{SEQ}</t>
+  </si>
+  <si>
+    <t>V{version}，version在同一plan_id下，自然增长（1,2,3, ..., N）</t>
+  </si>
+  <si>
+    <t>8Pro-01，格式：PP-{SKU}-{COLOR}-{SIZE}-{SEQ}</t>
+  </si>
+  <si>
+    <t>8Pro-01，格式：PP-{SKU}-{COLOR}-{SIZE}</t>
+  </si>
+  <si>
+    <t>version在同一plan_id下，自然增长（1,2,3, ..., N）</t>
+  </si>
+  <si>
+    <t>关联生产准备指令集版本号，类型: int</t>
   </si>
 </sst>
 </file>
@@ -903,7 +921,7 @@
   <numFmts count="1">
     <numFmt numFmtId="300" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -966,6 +984,16 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
@@ -1475,9 +1503,9 @@
     </border>
   </borders>
   <cellStyleXfs>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1488,7 +1516,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="300" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1633,13 +1661,13 @@
     <xf numFmtId="300" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="300" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1660,25 +1688,25 @@
     <xf numFmtId="300" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="11" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="300" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1756,8 +1784,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="300" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="300" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="300" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2058,10 +2119,10 @@
   <dimension ref="D62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" style="94" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.832" style="95" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.1641" style="95" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="78.5" style="95" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="105" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.832" style="106" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.1641" style="106" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.5" style="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" customHeight="1">
@@ -2763,10 +2824,10 @@
   <dimension ref="D64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" style="94" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.832" style="95" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.832" style="95" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" style="95" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="105" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.832" style="106" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.832" style="106" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.5" style="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" customHeight="1">
@@ -2803,20 +2864,20 @@
       <c r="C4" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>94</v>
+      <c r="D4" s="86" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" s="4" t="s"/>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="95" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>95</v>
+      <c r="D5" s="97" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.75" customHeight="1">
@@ -3480,13 +3541,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="D70"/>
+  <dimension ref="D73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" style="94" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.832" style="95" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6641" style="95" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.832" style="95" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="105" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.832" style="106" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6641" style="106" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.832" style="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" customHeight="1">
@@ -3590,93 +3651,93 @@
     <row r="10" spans="1:4" ht="19.5" customHeight="1">
       <c r="A10" s="4" t="s"/>
       <c r="B10" s="39" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" customHeight="1">
       <c r="A11" s="4" t="s"/>
       <c r="B11" s="39" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="19.5" customHeight="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20.25" customHeight="1">
       <c r="A12" s="4" t="s"/>
-      <c r="B12" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="20.25" customHeight="1">
+      <c r="B12" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19.5" customHeight="1">
       <c r="A13" s="4" t="s"/>
-      <c r="B13" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B13" s="5" t="s"/>
+      <c r="C13" s="5" t="s"/>
+      <c r="D13" s="5" t="s"/>
+    </row>
+    <row r="14" spans="1:4" ht="18.75" customHeight="1">
       <c r="A14" s="4" t="s"/>
       <c r="B14" s="5" t="s"/>
       <c r="C14" s="5" t="s"/>
       <c r="D14" s="5" t="s"/>
     </row>
-    <row r="15" spans="1:4" ht="18.75" customHeight="1">
+    <row r="15" spans="1:4" ht="21.75" customHeight="1">
       <c r="A15" s="4" t="s"/>
-      <c r="B15" s="5" t="s"/>
-      <c r="C15" s="5" t="s"/>
-      <c r="D15" s="5" t="s"/>
-    </row>
-    <row r="16" spans="1:4" ht="21.75" customHeight="1">
+      <c r="B15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="7" t="s"/>
+      <c r="D15" s="8" t="s"/>
+    </row>
+    <row r="16" spans="1:4" ht="18.75" customHeight="1">
       <c r="A16" s="4" t="s"/>
-      <c r="B16" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="7" t="s"/>
-      <c r="D16" s="8" t="s"/>
-    </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1">
+      <c r="B16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="21.75" customHeight="1">
       <c r="A17" s="4" t="s"/>
-      <c r="B17" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>4</v>
+      <c r="B17" s="103" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="21.75" customHeight="1">
       <c r="A18" s="4" t="s"/>
-      <c r="B18" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>210</v>
+      <c r="B18" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="102" t="s">
+        <v>296</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="21.75" customHeight="1">
@@ -3905,8 +3966,8 @@
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1">
       <c r="A39" s="4" t="s"/>
-      <c r="B39" s="12" t="s">
-        <v>208</v>
+      <c r="B39" s="103" t="s">
+        <v>188</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>209</v>
@@ -3917,105 +3978,111 @@
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1">
       <c r="A40" s="4" t="s"/>
-      <c r="B40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>213</v>
+      <c r="B40" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" s="102" t="s">
+        <v>296</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1">
       <c r="A41" s="4" t="s"/>
-      <c r="B41" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>230</v>
+      <c r="B41" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1">
       <c r="A42" s="4" t="s"/>
       <c r="B42" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1">
       <c r="A43" s="4" t="s"/>
       <c r="B43" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
       <c r="A44" s="4" t="s"/>
       <c r="B44" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1">
       <c r="A45" s="4" t="s"/>
       <c r="B45" s="9" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1">
       <c r="A46" s="4" t="s"/>
       <c r="B46" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1">
       <c r="A47" s="4" t="s"/>
-      <c r="B47" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>224</v>
+      <c r="B47" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1">
       <c r="A48" s="4" t="s"/>
-      <c r="B48" s="5" t="s"/>
-      <c r="C48" s="5" t="s"/>
-      <c r="D48" s="5" t="s"/>
+      <c r="B48" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1">
       <c r="A49" s="4" t="s"/>
@@ -4025,243 +4092,273 @@
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1">
       <c r="A50" s="4" t="s"/>
-      <c r="B50" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="C50" s="51" t="s"/>
-      <c r="D50" s="52" t="s"/>
+      <c r="B50" s="5" t="s"/>
+      <c r="C50" s="5" t="s"/>
+      <c r="D50" s="5" t="s"/>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1">
       <c r="A51" s="4" t="s"/>
-      <c r="B51" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>4</v>
-      </c>
+      <c r="B51" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="C51" s="51" t="s"/>
+      <c r="D51" s="52" t="s"/>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1">
       <c r="A52" s="4" t="s"/>
-      <c r="B52" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>226</v>
+      <c r="B52" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1">
       <c r="A53" s="4" t="s"/>
-      <c r="B53" s="12" t="s">
-        <v>244</v>
+      <c r="B53" s="103" t="s">
+        <v>188</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>213</v>
+        <v>209</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1">
       <c r="A54" s="4" t="s"/>
-      <c r="B54" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>245</v>
+      <c r="B54" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="C54" s="102" t="s">
+        <v>296</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1">
       <c r="A55" s="4" t="s"/>
-      <c r="B55" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>246</v>
+      <c r="B55" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1">
       <c r="A56" s="4" t="s"/>
       <c r="B56" s="9" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>247</v>
+        <v>23</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1">
       <c r="A57" s="4" t="s"/>
       <c r="B57" s="9" t="s">
-        <v>249</v>
+        <v>25</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>250</v>
+        <v>26</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1">
       <c r="A58" s="4" t="s"/>
       <c r="B58" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1">
       <c r="A59" s="4" t="s"/>
-      <c r="B59" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>224</v>
+      <c r="B59" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1">
       <c r="A60" s="4" t="s"/>
-      <c r="B60" s="5" t="s"/>
-      <c r="C60" s="5" t="s"/>
-      <c r="D60" s="5" t="s"/>
+      <c r="B60" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="61" spans="1:4" ht="18" customHeight="1">
       <c r="A61" s="4" t="s"/>
-      <c r="B61" s="5" t="s"/>
-      <c r="C61" s="5" t="s"/>
-      <c r="D61" s="5" t="s"/>
+      <c r="B61" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="62" spans="1:4" ht="18" customHeight="1">
       <c r="A62" s="4" t="s"/>
-      <c r="B62" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C62" s="7" t="s"/>
-      <c r="D62" s="8" t="s"/>
+      <c r="B62" s="5" t="s"/>
+      <c r="C62" s="5" t="s"/>
+      <c r="D62" s="5" t="s"/>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="4" t="s"/>
-      <c r="B63" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>4</v>
-      </c>
+      <c r="B63" s="5" t="s"/>
+      <c r="C63" s="5" t="s"/>
+      <c r="D63" s="5" t="s"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="4" t="s"/>
-      <c r="B64" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>226</v>
-      </c>
+      <c r="B64" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="7" t="s"/>
+      <c r="D64" s="8" t="s"/>
     </row>
     <row r="65" spans="1:4" ht="18" customHeight="1">
       <c r="A65" s="4" t="s"/>
-      <c r="B65" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>255</v>
+      <c r="B65" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="4" t="s"/>
-      <c r="B66" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>257</v>
+      <c r="B66" s="103" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18" customHeight="1">
       <c r="A67" s="4" t="s"/>
-      <c r="B67" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>259</v>
+      <c r="B67" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="102" t="s">
+        <v>296</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="18" customHeight="1">
       <c r="A68" s="4" t="s"/>
-      <c r="B68" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>261</v>
+      <c r="B68" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="18" customHeight="1">
       <c r="A69" s="4" t="s"/>
       <c r="B69" s="9" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="18" customHeight="1">
       <c r="A70" s="4" t="s"/>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18" customHeight="1">
+      <c r="A71" s="4" t="s"/>
+      <c r="B71" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18" customHeight="1">
+      <c r="A72" s="4" t="s"/>
+      <c r="B72" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18" customHeight="1">
+      <c r="A73" s="4" t="s"/>
+      <c r="B73" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C73" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D73" s="17" t="s">
         <v>224</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B64:D64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
